--- a/TP/TP1 TablasLibro1.xlsx
+++ b/TP/TP1 TablasLibro1.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Curso TSDS\4C\Ingenieria\TP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3222989-A6F1-4DA9-B820-5F5619D8034B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C184E806-CFA9-45F5-A989-0AF791A23A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9190" yWindow="2570" windowWidth="24810" windowHeight="17500" activeTab="1" xr2:uid="{F1BDCCEC-0E38-45AB-A349-98AAC21C2264}"/>
+    <workbookView xWindow="10670" yWindow="2460" windowWidth="24810" windowHeight="17500" activeTab="2" xr2:uid="{F1BDCCEC-0E38-45AB-A349-98AAC21C2264}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="85">
   <si>
     <t>Concepto del curso</t>
   </si>
@@ -185,6 +186,135 @@
   </si>
   <si>
     <t>Sin integración con stock real; anotan en cuadernos separados.</t>
+  </si>
+  <si>
+    <t>Proceso</t>
+  </si>
+  <si>
+    <t>Problema principal</t>
+  </si>
+  <si>
+    <t>Compras</t>
+  </si>
+  <si>
+    <t>Don Roberto decide por intuición, ordena verbalmente, anotación manual.</t>
+  </si>
+  <si>
+    <t>Sobreestock, quiebres, vencimientos.</t>
+  </si>
+  <si>
+    <t>Recepción de mercadería</t>
+  </si>
+  <si>
+    <t>Se anota en fichas sin control de lotes ni fechas.</t>
+  </si>
+  <si>
+    <t>Pérdida de trazabilidad.</t>
+  </si>
+  <si>
+    <t>Gestión de cuentas corrientes</t>
+  </si>
+  <si>
+    <t>Fichas y cuadernos, sin integración con despachos.</t>
+  </si>
+  <si>
+    <t>Morosidad, flujo de caja impredecible.</t>
+  </si>
+  <si>
+    <t>Despacho a clientes</t>
+  </si>
+  <si>
+    <t>Se preparan pedidos según lo que "se cree que hay".</t>
+  </si>
+  <si>
+    <t>Errores, faltantes, clientes insatisfechos.</t>
+  </si>
+  <si>
+    <t>Elemento</t>
+  </si>
+  <si>
+    <t>Entradas</t>
+  </si>
+  <si>
+    <t>Experiencia de Don Roberto, ofertas informales de proveedores, necesidad percibida por quiebres.</t>
+  </si>
+  <si>
+    <t>Salidas</t>
+  </si>
+  <si>
+    <t>Mercadería recibida (con datos incompletos), facturas proveedor, anotaciones manuales.</t>
+  </si>
+  <si>
+    <t>Actividades</t>
+  </si>
+  <si>
+    <t>1. Detectar necesidad (intuitiva). 2. Contactar proveedor. 3. Acordar precio y cantidad verbalmente. 4. Recibir mercadería. 5. Anotar en cuaderno.</t>
+  </si>
+  <si>
+    <t>Responsables</t>
+  </si>
+  <si>
+    <t>Don Roberto (decide), empleado de depósito (recibe y anota).</t>
+  </si>
+  <si>
+    <t>Puntos débiles</t>
+  </si>
+  <si>
+    <t>• Sin cálculo de punto de pedido. • Sin registro de lotes/vencimientos. • Órdenes verbales = errores de comunicación. • No hay relación entre compras y rotación real. • Pérdidas por productos vencidos no cuantificadas.</t>
+  </si>
+  <si>
+    <t>Mejora</t>
+  </si>
+  <si>
+    <t>Principio sistémico aplicado</t>
+  </si>
+  <si>
+    <t>Justificación</t>
+  </si>
+  <si>
+    <t>Cálculo automático de stock mínimo</t>
+  </si>
+  <si>
+    <t>Retroalimentación (feedback)</t>
+  </si>
+  <si>
+    <t>El sistema usa datos históricos de ventas para ajustar compras, rompiendo el circuito de intuición.</t>
+  </si>
+  <si>
+    <t>Alertas antes del quiebre</t>
+  </si>
+  <si>
+    <t>Control preventivo</t>
+  </si>
+  <si>
+    <t>Evita la pérdida de ventas y la insatisfacción del cliente.</t>
+  </si>
+  <si>
+    <t>Registro de lotes con FEFO</t>
+  </si>
+  <si>
+    <t>Sinergia</t>
+  </si>
+  <si>
+    <t>Integra compras con despachos: el mismo dato sirve para comprar y para vender en orden.</t>
+  </si>
+  <si>
+    <t>Don Roberto puede anular, pero queda registro</t>
+  </si>
+  <si>
+    <t>Totalidad</t>
+  </si>
+  <si>
+    <t>Se respeta experiencia pero se hace visible el impacto de sus decisiones en el sistema global.</t>
+  </si>
+  <si>
+    <t>Orden de compra digital</t>
+  </si>
+  <si>
+    <t>Estabilidad y homeostasis</t>
+  </si>
+  <si>
+    <t>Elimina ambigüedad de lo verbal; todos los actores ven la misma información.</t>
   </si>
 </sst>
 </file>
@@ -280,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -308,6 +438,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -739,15 +875,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6699E924-DE45-4A3A-828D-A9491C72FF26}">
-  <dimension ref="B2:D7"/>
+  <dimension ref="B2:H7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.26953125" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="38.08984375" customWidth="1"/>
+    <col min="6" max="6" width="23.08984375" customWidth="1"/>
+    <col min="7" max="7" width="41.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="8" t="s">
         <v>24</v>
       </c>
@@ -757,8 +896,17 @@
       <c r="D2" s="8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="9" t="s">
         <v>27</v>
       </c>
@@ -768,8 +916,17 @@
       <c r="D3" s="7" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="9" t="s">
         <v>30</v>
       </c>
@@ -779,8 +936,17 @@
       <c r="D4" s="7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="9" t="s">
         <v>33</v>
       </c>
@@ -790,8 +956,17 @@
       <c r="D5" s="7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F5" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="9" t="s">
         <v>36</v>
       </c>
@@ -801,8 +976,17 @@
       <c r="D6" s="7" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F6" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="9" t="s">
         <v>39</v>
       </c>
@@ -811,6 +995,125 @@
       </c>
       <c r="D7" s="7" t="s">
         <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF24C936-0026-4428-AFA0-DFCD5175664D}">
+  <dimension ref="B2:G7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="20.6328125" customWidth="1"/>
+    <col min="3" max="3" width="80.90625" customWidth="1"/>
+    <col min="5" max="5" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.54296875" customWidth="1"/>
+    <col min="7" max="7" width="50.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
